--- a/downloads/controle-financeiro-planilha.xlsx
+++ b/downloads/controle-financeiro-planilha.xlsx
@@ -676,7 +676,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>A planilha não tem PIN próprio (vale a segurança da sua conta Google), voz, foto de nota nem captura de notificações. Para isso, use o app no Android.</t>
+          <t>A planilha não tem PIN próprio (vale a segurança da sua conta Google), voz nem foto de nota. Para isso, use o app no Android.</t>
         </is>
       </c>
     </row>

--- a/downloads/controle-financeiro-planilha.xlsx
+++ b/downloads/controle-financeiro-planilha.xlsx
@@ -562,7 +562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Controle Financeiro: planilha</t>
+          <t>Controle Financeiro Privado: planilha</t>
         </is>
       </c>
     </row>
